--- a/branches/master/ValueSet-mii-vs-icu-body-site-observation-monitoring-und-vitaldaten.xlsx
+++ b/branches/master/ValueSet-mii-vs-icu-body-site-observation-monitoring-und-vitaldaten.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>
